--- a/branches/migration/fresh-20260806/all-profiles.xlsx
+++ b/branches/migration/fresh-20260806/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T16:02:43+00:00</t>
+    <t>2026-08-06T18:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
